--- a/outputs/reports/easy_ensemble_v1/evaluation.xlsx
+++ b/outputs/reports/easy_ensemble_v1/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7351293133790424</v>
+        <v>0.7001155034727534</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01008021954823728</v>
+        <v>0.008642867100077304</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7717171717171717</v>
+        <v>0.7893518518518519</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01990049751243781</v>
+        <v>0.01709851704210698</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7350013774785784</v>
+        <v>0.6998196469685342</v>
       </c>
       <c r="G2" t="n">
-        <v>104049</v>
+        <v>182373</v>
       </c>
       <c r="H2" t="n">
-        <v>37514</v>
+        <v>78227</v>
       </c>
       <c r="I2" t="n">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="J2" t="n">
-        <v>382</v>
+        <v>682</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8431200100294425</v>
+        <v>0.8350163285047327</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06182051370602611</v>
+        <v>0.0356554341176023</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003484492249644511</v>
+        <v>0.003304470213872656</v>
       </c>
       <c r="C2" t="n">
-        <v>1421</v>
+        <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06052076002814919</v>
+        <v>0.05736137667304015</v>
       </c>
       <c r="E2" t="n">
-        <v>17.36860227894711</v>
+        <v>17.35872105374973</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1737373737373737</v>
+        <v>0.1736111111111111</v>
       </c>
       <c r="G2" t="n">
-        <v>7103</v>
+        <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02843868787836126</v>
+        <v>0.02569986232216613</v>
       </c>
       <c r="I2" t="n">
-        <v>8.161501257826755</v>
+        <v>7.777301854401441</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4080808080808081</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="K2" t="n">
-        <v>14206</v>
+        <v>26147</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01752780515275236</v>
+        <v>0.01675144376027842</v>
       </c>
       <c r="M2" t="n">
-        <v>5.030232210888272</v>
+        <v>5.069328114973887</v>
       </c>
       <c r="N2" t="n">
-        <v>0.503030303030303</v>
+        <v>0.5069444444444444</v>
       </c>
     </row>
   </sheetData>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2756</v>
+        <v>4419</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23109</v>
+        <v>38778</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>4.327318360811805e-05</v>
+        <v>7.736345350456444e-05</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -772,13 +772,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>77847</v>
+        <v>138541</v>
       </c>
       <c r="C6" t="n">
-        <v>109</v>
+        <v>173</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001400182409084486</v>
+        <v>0.001248727813427072</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36689</v>
+        <v>75292</v>
       </c>
       <c r="C7" t="n">
-        <v>297</v>
+        <v>495</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008095069366840197</v>
+        <v>0.0065744036551028</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -810,13 +810,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1571</v>
+        <v>4250</v>
       </c>
       <c r="C8" t="n">
-        <v>70</v>
+        <v>183</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04455760661998727</v>
+        <v>0.04305882352941177</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.07352941176470588</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>

--- a/outputs/reports/easy_ensemble_v1/evaluation.xlsx
+++ b/outputs/reports/easy_ensemble_v1/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7001155034727534</v>
+        <v>0.7619328091056513</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008642867100077304</v>
+        <v>0.01046101835462214</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7893518518518519</v>
+        <v>0.7726737338044759</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01709851704210698</v>
+        <v>0.02064256269863746</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6998196469685342</v>
+        <v>0.761897818621338</v>
       </c>
       <c r="G2" t="n">
-        <v>182373</v>
+        <v>198562</v>
       </c>
       <c r="H2" t="n">
-        <v>78227</v>
+        <v>62053</v>
       </c>
       <c r="I2" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="J2" t="n">
-        <v>682</v>
+        <v>656</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8350163285047327</v>
+        <v>0.852947825889866</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0356554341176023</v>
+        <v>0.0425594226276183</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003304470213872656</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C2" t="n">
         <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05736137667304015</v>
+        <v>0.07074569789674952</v>
       </c>
       <c r="E2" t="n">
-        <v>17.35872105374973</v>
+        <v>21.78734176074878</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1736111111111111</v>
+        <v>0.2179034157832744</v>
       </c>
       <c r="G2" t="n">
         <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02569986232216613</v>
+        <v>0.02852990668502371</v>
       </c>
       <c r="I2" t="n">
-        <v>7.777301854401441</v>
+        <v>8.786270343336913</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.4393404004711425</v>
       </c>
       <c r="K2" t="n">
         <v>26147</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01675144376027842</v>
+        <v>0.01946686044288064</v>
       </c>
       <c r="M2" t="n">
-        <v>5.069328114973887</v>
+        <v>5.995150999808413</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5069444444444444</v>
+        <v>0.5995288574793876</v>
       </c>
     </row>
   </sheetData>
@@ -715,16 +715,12 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -734,7 +730,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4419</v>
+        <v>1520</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -753,13 +749,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38778</v>
+        <v>46231</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>7.736345350456444e-05</v>
+        <v>0.0001297830460080898</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -772,13 +768,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>138541</v>
+        <v>150337</v>
       </c>
       <c r="C6" t="n">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001248727813427072</v>
+        <v>0.001223916933289875</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -791,13 +787,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>75292</v>
+        <v>60571</v>
       </c>
       <c r="C7" t="n">
-        <v>495</v>
+        <v>469</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0065744036551028</v>
+        <v>0.007742979313532879</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -810,13 +806,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4250</v>
+        <v>2579</v>
       </c>
       <c r="C8" t="n">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04305882352941177</v>
+        <v>0.0612640558355952</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -829,13 +825,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>226</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07352941176470588</v>
+        <v>0.1415929203539823</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>

--- a/outputs/reports/easy_ensemble_v1/evaluation.xlsx
+++ b/outputs/reports/easy_ensemble_v1/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7619328091056513</v>
+        <v>0.7987811203319503</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01046101835462214</v>
+        <v>0.01568277444855285</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7726737338044759</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02064256269863746</v>
+        <v>0.03073079325421612</v>
       </c>
       <c r="F2" t="n">
-        <v>0.761897818621338</v>
+        <v>0.7989478618678056</v>
       </c>
       <c r="G2" t="n">
-        <v>198562</v>
+        <v>30678</v>
       </c>
       <c r="H2" t="n">
-        <v>62053</v>
+        <v>7720</v>
       </c>
       <c r="I2" t="n">
-        <v>193</v>
+        <v>39</v>
       </c>
       <c r="J2" t="n">
-        <v>656</v>
+        <v>123</v>
       </c>
       <c r="K2" t="n">
-        <v>0.852947825889866</v>
+        <v>0.8633574022309547</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0425594226276183</v>
+        <v>0.08791616639087821</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C2" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07074569789674952</v>
+        <v>0.08808290155440414</v>
       </c>
       <c r="E2" t="n">
-        <v>21.78734176074878</v>
+        <v>20.96590545640632</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2179034157832744</v>
+        <v>0.2098765432098765</v>
       </c>
       <c r="G2" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02852990668502371</v>
+        <v>0.04460580912863071</v>
       </c>
       <c r="I2" t="n">
-        <v>8.786270343336913</v>
+        <v>10.61728395061728</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4393404004711425</v>
+        <v>0.5308641975308642</v>
       </c>
       <c r="K2" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01946686044288064</v>
+        <v>0.02826763485477178</v>
       </c>
       <c r="M2" t="n">
-        <v>5.995150999808413</v>
+        <v>6.728395061728396</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5995288574793876</v>
+        <v>0.6728395061728395</v>
       </c>
     </row>
   </sheetData>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1520</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46231</v>
+        <v>7060</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001297830460080898</v>
+        <v>0</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -768,13 +768,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>150337</v>
+        <v>23546</v>
       </c>
       <c r="C6" t="n">
-        <v>184</v>
+        <v>39</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001223916933289875</v>
+        <v>0.001656332285738554</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60571</v>
+        <v>7815</v>
       </c>
       <c r="C7" t="n">
-        <v>469</v>
+        <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007742979313532879</v>
+        <v>0.0127959053103007</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2579</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>158</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0612640558355952</v>
+        <v>0.1782945736434109</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -825,16 +825,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>226</v>
-      </c>
-      <c r="C9" t="n">
-        <v>32</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1415929203539823</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
